--- a/Team-Data/2008-09/11-6-2008-09.xlsx
+++ b/Team-Data/2008-09/11-6-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
         <v>9</v>
@@ -763,13 +830,13 @@
         <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
         <v>30</v>
@@ -784,28 +851,28 @@
         <v>2</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>4</v>
       </c>
       <c r="AU2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -843,97 +910,97 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="J3" t="n">
-        <v>77.8</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M3" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.281</v>
+        <v>0.268</v>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="P3" t="n">
-        <v>31</v>
+        <v>31.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="S3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="T3" t="n">
-        <v>49</v>
+        <v>46.4</v>
       </c>
       <c r="U3" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="V3" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="W3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="AA3" t="n">
         <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>93.5</v>
+        <v>92.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>5</v>
       </c>
       <c r="AG3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -942,61 +1009,61 @@
         <v>22</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1170,22 @@
         <v>-6.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
         <v>30</v>
@@ -1139,10 +1206,10 @@
         <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
         <v>7</v>
@@ -1154,13 +1221,13 @@
         <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>25</v>
@@ -1169,16 +1236,16 @@
         <v>25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>27</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -1207,160 +1274,160 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>31.5</v>
+        <v>32.2</v>
       </c>
       <c r="J5" t="n">
-        <v>83.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.378</v>
+        <v>0.4</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.377</v>
+        <v>0.384</v>
       </c>
       <c r="O5" t="n">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="P5" t="n">
-        <v>26.3</v>
+        <v>29.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.829</v>
+        <v>0.805</v>
       </c>
       <c r="R5" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="S5" t="n">
-        <v>31.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>44</v>
+        <v>43.2</v>
       </c>
       <c r="U5" t="n">
-        <v>16</v>
+        <v>18.2</v>
       </c>
       <c r="V5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>23</v>
+        <v>24.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>90.5</v>
+        <v>94</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5.8</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="n">
         <v>9</v>
       </c>
-      <c r="AE5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>11</v>
-      </c>
       <c r="AI5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="n">
         <v>9</v>
       </c>
       <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
         <v>7</v>
       </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT5" t="n">
         <v>11</v>
       </c>
-      <c r="AT5" t="n">
-        <v>8</v>
-      </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -1389,160 +1456,160 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>35.8</v>
+        <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>77</v>
+        <v>75.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.464</v>
+        <v>0.457</v>
       </c>
       <c r="L6" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.356</v>
+        <v>0.33</v>
       </c>
       <c r="O6" t="n">
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
       <c r="P6" t="n">
-        <v>28.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R6" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="S6" t="n">
         <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>45</v>
+        <v>44.2</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="V6" t="n">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>22.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>98.8</v>
+        <v>96</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" t="n">
         <v>9</v>
       </c>
-      <c r="AE6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
         <v>11</v>
       </c>
-      <c r="AI6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP6" t="n">
         <v>8</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>20</v>
       </c>
       <c r="AR6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX6" t="n">
         <v>14</v>
       </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3</v>
-      </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -1649,22 +1716,22 @@
         <v>-0.5</v>
       </c>
       <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
         <v>9</v>
       </c>
-      <c r="AE7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>11</v>
-      </c>
       <c r="AI7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ7" t="n">
         <v>16</v>
@@ -1673,7 +1740,7 @@
         <v>13</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM7" t="n">
         <v>16</v>
@@ -1682,25 +1749,25 @@
         <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR7" t="n">
         <v>24</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT7" t="n">
         <v>20</v>
       </c>
       <c r="AU7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV7" t="n">
         <v>2</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>20</v>
       </c>
       <c r="AF8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
         <v>22</v>
@@ -1846,10 +1913,10 @@
         <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK8" t="n">
         <v>12</v>
@@ -1861,10 +1928,10 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP8" t="n">
         <v>4</v>
@@ -1876,7 +1943,7 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
         <v>5</v>
@@ -1891,7 +1958,7 @@
         <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY8" t="n">
         <v>28</v>
@@ -1900,13 +1967,13 @@
         <v>28</v>
       </c>
       <c r="BA8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2080,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
         <v>9</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>11</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2043,19 +2110,19 @@
         <v>25</v>
       </c>
       <c r="AN9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ9" t="n">
         <v>3</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>19</v>
@@ -2073,7 +2140,7 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-0.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>9</v>
@@ -2219,7 +2286,7 @@
         <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM10" t="n">
         <v>4</v>
@@ -2228,13 +2295,13 @@
         <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP10" t="n">
         <v>5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AR10" t="n">
         <v>1</v>
@@ -2243,19 +2310,19 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" t="n">
-        <v>79.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.416</v>
+        <v>0.401</v>
       </c>
       <c r="L11" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M11" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.356</v>
+        <v>0.333</v>
       </c>
       <c r="O11" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="P11" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.863</v>
+        <v>0.871</v>
       </c>
       <c r="R11" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>33.2</v>
+        <v>33.8</v>
       </c>
       <c r="T11" t="n">
-        <v>43</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="X11" t="n">
         <v>2</v>
@@ -2365,94 +2432,94 @@
         <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.2</v>
+        <v>95.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AJ11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AM11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN11" t="n">
         <v>13</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>11</v>
       </c>
       <c r="AO11" t="n">
         <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
         <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -2559,52 +2626,52 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
       </c>
       <c r="AF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL12" t="n">
         <v>11</v>
       </c>
-      <c r="AG12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AM12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN12" t="n">
         <v>16</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AO12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP12" t="n">
         <v>12</v>
       </c>
-      <c r="AM12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
         <v>26</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
         <v>19</v>
@@ -2613,13 +2680,13 @@
         <v>24</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY12" t="n">
         <v>30</v>
@@ -2628,10 +2695,10 @@
         <v>25</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC12" t="n">
         <v>15</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-20.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>29</v>
@@ -2753,28 +2820,28 @@
         <v>29</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
         <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN13" t="n">
         <v>25</v>
       </c>
       <c r="AO13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
@@ -2783,13 +2850,13 @@
         <v>26</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
         <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU13" t="n">
         <v>25</v>
@@ -2801,10 +2868,10 @@
         <v>23</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -2845,10 +2912,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2860,113 +2927,113 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="J14" t="n">
-        <v>84</v>
+        <v>82.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.425</v>
+        <v>0.435</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="M14" t="n">
-        <v>19.3</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>0.414</v>
+        <v>0.456</v>
       </c>
       <c r="O14" t="n">
-        <v>29.7</v>
+        <v>26</v>
       </c>
       <c r="P14" t="n">
-        <v>40.3</v>
+        <v>34.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.736</v>
+        <v>0.748</v>
       </c>
       <c r="R14" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="S14" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="T14" t="n">
-        <v>52.7</v>
+        <v>51.8</v>
       </c>
       <c r="U14" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="V14" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="X14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
         <v>9</v>
       </c>
-      <c r="X14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>109</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>11</v>
-      </c>
       <c r="AI14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AJ14" t="n">
         <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AN14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR14" t="n">
         <v>6</v>
       </c>
-      <c r="AO14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4</v>
-      </c>
       <c r="AS14" t="n">
         <v>1</v>
       </c>
@@ -2974,28 +3041,28 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV14" t="n">
         <v>15</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AY14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -3105,25 +3172,25 @@
         <v>-2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
         <v>28</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3138,10 +3205,10 @@
         <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3150,25 +3217,25 @@
         <v>17</v>
       </c>
       <c r="AS15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
       </c>
       <c r="AV15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX15" t="n">
         <v>19</v>
       </c>
-      <c r="AW15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>21</v>
-      </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>16</v>
@@ -3180,7 +3247,7 @@
         <v>28</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -3287,46 +3354,46 @@
         <v>7.8</v>
       </c>
       <c r="AD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
         <v>9</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AK16" t="n">
         <v>10</v>
       </c>
       <c r="AL16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP16" t="n">
         <v>6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3347,22 +3414,22 @@
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
         <v>2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
         <v>4</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -3391,97 +3458,97 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="I17" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="L17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.322</v>
+        <v>0.342</v>
       </c>
       <c r="O17" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="P17" t="n">
-        <v>25.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.673</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="S17" t="n">
-        <v>32.5</v>
+        <v>29.8</v>
       </c>
       <c r="T17" t="n">
-        <v>43.8</v>
+        <v>41.4</v>
       </c>
       <c r="U17" t="n">
-        <v>24.8</v>
+        <v>24</v>
       </c>
       <c r="V17" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="W17" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.5</v>
+        <v>25.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.8</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>97.8</v>
+        <v>97.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH17" t="n">
         <v>6</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>4</v>
       </c>
       <c r="AI17" t="n">
         <v>5</v>
@@ -3490,61 +3557,61 @@
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
         <v>28</v>
       </c>
       <c r="AR17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS17" t="n">
         <v>18</v>
       </c>
-      <c r="AS17" t="n">
-        <v>8</v>
-      </c>
       <c r="AT17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
       </c>
       <c r="AV17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX17" t="n">
         <v>24</v>
       </c>
-      <c r="AW17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>22</v>
-      </c>
       <c r="AY17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
         <v>27</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>20</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
         <v>22</v>
@@ -3672,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL18" t="n">
         <v>27</v>
@@ -3681,31 +3748,31 @@
         <v>26</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3714,7 +3781,7 @@
         <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ18" t="n">
         <v>17</v>
@@ -3726,7 +3793,7 @@
         <v>12</v>
       </c>
       <c r="BC18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -3833,46 +3900,46 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP19" t="n">
         <v>19</v>
       </c>
-      <c r="AO19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
         <v>19</v>
@@ -3887,10 +3954,10 @@
         <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
         <v>2</v>
@@ -3908,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -4015,31 +4082,31 @@
         <v>5.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
         <v>7</v>
       </c>
       <c r="AL20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM20" t="n">
         <v>10</v>
@@ -4048,13 +4115,13 @@
         <v>2</v>
       </c>
       <c r="AO20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP20" t="n">
         <v>15</v>
       </c>
-      <c r="AP20" t="n">
-        <v>16</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>24</v>
@@ -4063,7 +4130,7 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
@@ -4072,19 +4139,19 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>5</v>
       </c>
-      <c r="AX20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4</v>
-      </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
         <v>8</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -4197,28 +4264,28 @@
         <v>-7.3</v>
       </c>
       <c r="AD21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="n">
         <v>9</v>
       </c>
-      <c r="AE21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>11</v>
-      </c>
       <c r="AI21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ21" t="n">
         <v>3</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,31 +4294,31 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
       </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>2</v>
@@ -4263,7 +4330,7 @@
         <v>4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>28</v>
@@ -4272,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -4379,28 +4446,28 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>20</v>
       </c>
       <c r="AF22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG22" t="n">
         <v>22</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI22" t="n">
         <v>24</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
         <v>29</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>29</v>
@@ -4421,22 +4488,22 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV22" t="n">
         <v>18</v>
       </c>
-      <c r="AT22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>19</v>
-      </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>15</v>
@@ -4445,16 +4512,16 @@
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB22" t="n">
         <v>30</v>
       </c>
       <c r="BC22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -4483,139 +4550,139 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
         <v>48</v>
       </c>
       <c r="I23" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="J23" t="n">
-        <v>79.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>0.437</v>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="M23" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.313</v>
+        <v>0.301</v>
       </c>
       <c r="O23" t="n">
-        <v>18.8</v>
+        <v>19.8</v>
       </c>
       <c r="P23" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.667</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>31</v>
       </c>
       <c r="T23" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="U23" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="V23" t="n">
-        <v>15.2</v>
+        <v>16.5</v>
       </c>
       <c r="W23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="X23" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>22.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.8</v>
+        <v>96.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT23" t="n">
         <v>7</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
         <v>9</v>
@@ -4624,19 +4691,19 @@
         <v>1</v>
       </c>
       <c r="AY23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB23" t="n">
         <v>17</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>19</v>
-      </c>
       <c r="BC23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -4665,160 +4732,160 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
       <c r="J24" t="n">
-        <v>83.5</v>
+        <v>81.2</v>
       </c>
       <c r="K24" t="n">
-        <v>0.447</v>
+        <v>0.463</v>
       </c>
       <c r="L24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M24" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.384</v>
+        <v>0.406</v>
       </c>
       <c r="O24" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="P24" t="n">
-        <v>22.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.763</v>
+        <v>0.754</v>
       </c>
       <c r="R24" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="S24" t="n">
-        <v>34.7</v>
+        <v>34.2</v>
       </c>
       <c r="T24" t="n">
-        <v>49.7</v>
+        <v>48.8</v>
       </c>
       <c r="U24" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="V24" t="n">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="W24" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="AD24" t="n">
         <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF24" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AG24" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI24" t="n">
         <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AL24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN24" t="n">
         <v>8</v>
       </c>
       <c r="AO24" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
         <v>2</v>
       </c>
       <c r="AU24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AW24" t="n">
         <v>29</v>
       </c>
       <c r="AX24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>1</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BB24" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BC24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4937,7 +5004,7 @@
         <v>5</v>
       </c>
       <c r="AH25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
@@ -4955,16 +5022,16 @@
         <v>15</v>
       </c>
       <c r="AN25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>29</v>
@@ -4979,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
         <v>21</v>
@@ -4991,16 +5058,16 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -5032,157 +5099,157 @@
         <v>4</v>
       </c>
       <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>34</v>
+      </c>
+      <c r="J26" t="n">
+        <v>80</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="O26" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="R26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>92</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL26" t="n">
         <v>2</v>
       </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>37</v>
-      </c>
-      <c r="J26" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="L26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M26" t="n">
-        <v>19</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="O26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="R26" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>37</v>
-      </c>
-      <c r="U26" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V26" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="W26" t="n">
-        <v>7</v>
-      </c>
-      <c r="X26" t="n">
+      <c r="AM26" t="n">
         <v>5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AN26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR26" t="n">
         <v>9</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>6</v>
       </c>
       <c r="AS26" t="n">
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU26" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AV26" t="n">
         <v>3</v>
       </c>
       <c r="AW26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX26" t="n">
         <v>21</v>
       </c>
-      <c r="AX26" t="n">
-        <v>18</v>
-      </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB26" t="n">
         <v>26</v>
       </c>
-      <c r="BB26" t="n">
-        <v>12</v>
-      </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -5289,25 +5356,25 @@
         <v>-15</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>20</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG27" t="n">
         <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI27" t="n">
         <v>15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
         <v>6</v>
@@ -5316,19 +5383,19 @@
         <v>22</v>
       </c>
       <c r="AM27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN27" t="n">
         <v>24</v>
       </c>
       <c r="AO27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP27" t="n">
         <v>24</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>27</v>
@@ -5352,16 +5419,16 @@
         <v>22</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA27" t="n">
         <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>-4.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>20</v>
       </c>
       <c r="AF28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG28" t="n">
         <v>22</v>
@@ -5489,7 +5556,7 @@
         <v>3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5501,28 +5568,28 @@
         <v>16</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
         <v>26</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT28" t="n">
         <v>24</v>
       </c>
       <c r="AU28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5534,7 +5601,7 @@
         <v>29</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ28" t="n">
         <v>11</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -5653,22 +5720,22 @@
         <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF29" t="n">
         <v>5</v>
       </c>
       <c r="AG29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH29" t="n">
         <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>28</v>
@@ -5680,7 +5747,7 @@
         <v>7</v>
       </c>
       <c r="AM29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="n">
         <v>1</v>
@@ -5689,7 +5756,7 @@
         <v>12</v>
       </c>
       <c r="AP29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5716,16 +5783,16 @@
         <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>12.3</v>
       </c>
       <c r="AD30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="n">
         <v>9</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>11</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5874,40 +5941,40 @@
         <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU30" t="n">
         <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX30" t="n">
         <v>27</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA30" t="n">
         <v>8</v>
       </c>
-      <c r="BA30" t="n">
-        <v>6</v>
-      </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6032,19 +6099,19 @@
         <v>3</v>
       </c>
       <c r="AI31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>19</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>20</v>
-      </c>
       <c r="AK31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL31" t="n">
         <v>28</v>
       </c>
       <c r="AM31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN31" t="n">
         <v>29</v>
@@ -6053,28 +6120,28 @@
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS31" t="n">
         <v>28</v>
       </c>
       <c r="AT31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
         <v>22</v>
@@ -6083,16 +6150,16 @@
         <v>29</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB31" t="n">
         <v>9</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-6-2008-09</t>
+          <t>2008-11-06</t>
         </is>
       </c>
     </row>
